--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
@@ -884,10 +884,10 @@
         <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
         <v>2.72</v>
@@ -896,22 +896,22 @@
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
@@ -920,73 +920,73 @@
         <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
       </c>
       <c r="AE2" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
         <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
         <v>8.199999999999999</v>
@@ -995,92 +995,92 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
         <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
         <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
         <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -881,7 +881,7 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
         <v>1.58</v>
@@ -899,7 +899,7 @@
         <v>5.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
         <v>1.64</v>
@@ -908,7 +908,7 @@
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>9.800000000000001</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>1.49</v>
@@ -881,25 +881,25 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.46</v>
+        <v>1.11</v>
       </c>
       <c r="O2" t="n">
         <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
         <v>1.64</v>
@@ -908,34 +908,34 @@
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
         <v>250</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -947,140 +947,140 @@
         <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
         <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AN2" t="n">
         <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 05:55:34</t>
+          <t>2026-06-23 08:02:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,166 +857,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
         <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.74</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.9</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>1.12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>1.24</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>1.24</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.6</v>
+        <v>1.19</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>1.24</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>1.24</v>
       </c>
       <c r="BF2" t="n">
-        <v>17.5</v>
+        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,254 +833,1016 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SC Grobina</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FK Auda</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:17:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BFC Daugavpils</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FK Riga</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:17:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SK Super Nova</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FK Jelgava</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:17:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Londrina</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="F5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>7.4</v>
       </c>
-      <c r="J2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
+      <c r="AS5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>1.04</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>1.04</v>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-23 10:10:04</t>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-23 12:17:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -896,19 +896,19 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1135,19 +1135,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
         <v>1.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
         <v>1.18</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1383,202 +1383,202 @@
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
         <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>
@@ -1643,13 +1643,13 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
         <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
         <v>2.72</v>
@@ -1715,10 +1715,10 @@
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AN5" t="n">
         <v>25</v>
@@ -1736,7 +1736,7 @@
         <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
@@ -1745,7 +1745,7 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW5" t="n">
         <v>8.199999999999999</v>
@@ -1757,7 +1757,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
         <v>8.199999999999999</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 12:17:29</t>
+          <t>2026-06-23 14:25:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1138,13 +1138,13 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q4" t="n">
         <v>1.3</v>
@@ -1404,7 +1404,7 @@
         <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,261 +1588,515 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 14:25:01</t>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:32:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Londrina</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>1.83</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H6" t="n">
         <v>5.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>6.4</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="J6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
         <v>1.13</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="N6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.58</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P6" t="n">
         <v>1.51</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>2.72</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1.17</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>5.9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2.36</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>1.64</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V6" t="n">
         <v>1.19</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="W6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X6" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y6" t="n">
         <v>14</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z6" t="n">
         <v>55</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA6" t="n">
         <v>250</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB6" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AC6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD6" t="n">
         <v>32</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE6" t="n">
         <v>160</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF6" t="n">
         <v>10</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH6" t="n">
         <v>36</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI6" t="n">
         <v>180</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ6" t="n">
         <v>23</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK6" t="n">
         <v>29</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL6" t="n">
         <v>70</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM6" t="n">
         <v>320</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN6" t="n">
         <v>25</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO6" t="n">
         <v>300</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP6" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AR6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT6" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU6" t="n">
         <v>7</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AV6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BA6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BE6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>17.5</v>
       </c>
-      <c r="BG5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
+      <c r="BG6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>1.04</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>1.04</v>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-23 14:25:01</t>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-23 16:32:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I5" t="n">
         <v>1.77</v>
@@ -1652,115 +1652,115 @@
         <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
         <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="V5" t="n">
         <v>2.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AP5" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>1.01</v>
@@ -1769,16 +1769,16 @@
         <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH5" t="n">
         <v>6.4</v>
@@ -1790,31 +1790,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>9.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BT5" t="n">
         <v>5.7</v>
@@ -1826,13 +1826,13 @@
         <v>11</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>
@@ -1873,166 +1873,166 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R6" t="n">
         <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
         <v>2.36</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>300</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>2.44</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.2</v>
+        <v>2.88</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>2.92</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,162 +1605,162 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>7.6</v>
+        <v>1.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>1.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
         <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
         <v>1.01</v>
@@ -1769,334 +1769,1096 @@
         <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Olympique Dcheira</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IRT Tanger</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-23 20:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CODM Meknes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HUSA Agadir</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-23 20:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-23 20:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Londrina</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="F9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H9" t="n">
         <v>5.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP9" t="n">
         <v>7.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BK9" t="n">
         <v>1.51</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-23 18:39:09</t>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1153,10 +1153,10 @@
         <v>1.18</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1377,19 +1377,19 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
         <v>1.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.09</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
@@ -1404,13 +1404,13 @@
         <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1885,10 +1885,10 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2139,10 +2139,10 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,498 +2367,1768 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>7.6</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.98</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 20:46:34</t>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wydad Casablanca</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MAS Maghrib A Fes</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:54:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Olympique Dcheira</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IRT Tanger</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>990</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>990</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:54:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Club R Zemamra</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:54:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CODM Meknes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HUSA Agadir</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>990</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>990</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:54:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:54:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Londrina</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F14" t="n">
         <v>1.83</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G14" t="n">
         <v>1.95</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H14" t="n">
         <v>5.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I14" t="n">
         <v>6.4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J14" t="n">
         <v>3.15</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L14" t="n">
         <v>1.56</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M14" t="n">
         <v>1.13</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N14" t="n">
         <v>2.48</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O14" t="n">
         <v>1.58</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P14" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q14" t="n">
         <v>2.74</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R14" t="n">
         <v>1.17</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S14" t="n">
         <v>5.9</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T14" t="n">
         <v>2.36</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U14" t="n">
         <v>1.63</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V14" t="n">
         <v>1.19</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W14" t="n">
         <v>2.06</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X14" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y14" t="n">
         <v>14</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z14" t="n">
         <v>46</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA14" t="n">
         <v>250</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB14" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC14" t="n">
         <v>8</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD14" t="n">
         <v>26</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE14" t="n">
         <v>160</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF14" t="n">
         <v>10</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI9" t="n">
+      <c r="AH14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI14" t="n">
         <v>180</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ14" t="n">
         <v>23</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK14" t="n">
         <v>29</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL14" t="n">
         <v>70</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM14" t="n">
         <v>330</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN14" t="n">
         <v>25</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AO14" t="n">
         <v>300</v>
       </c>
-      <c r="AP9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="AP14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR14" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT14" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AU14" t="n">
         <v>7</v>
       </c>
-      <c r="AV9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AX14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AY14" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="AZ14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BA14" t="n">
         <v>11.5</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB14" t="n">
         <v>19.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BC14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BE14" t="n">
         <v>12</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BF14" t="n">
         <v>21</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BG14" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
         <v>1.64</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BJ14" t="n">
         <v>18.5</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BK14" t="n">
         <v>1.51</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>1.64</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BN14" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BO14" t="n">
         <v>2.84</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BP14" t="n">
         <v>22</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BQ14" t="n">
         <v>1.53</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>1.6</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="BT14" t="n">
         <v>13</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="BU14" t="n">
         <v>1.46</v>
       </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
         <v>1.61</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>1.64</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>1.6</v>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-23 20:46:34</t>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-23 22:54:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1404,7 +1404,7 @@
         <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1646,7 +1646,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.25</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1900,7 +1900,7 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2154,7 +2154,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
@@ -2414,13 +2414,13 @@
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.45</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3170,31 +3170,31 @@
         <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.02</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -3427,7 +3427,7 @@
         <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
         <v>1.47</v>
@@ -3436,7 +3436,7 @@
         <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-23 22:54:32</t>
+          <t>2026-06-24 01:03:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>1.04</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>1.04</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>1.04</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
@@ -2420,7 +2420,7 @@
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>1.04</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q10" t="n">
         <v>1.29</v>
@@ -2928,7 +2928,7 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
         <v>1.5</v>
@@ -3191,7 +3191,7 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3445,7 +3445,7 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
         <v>2.06</v>
@@ -3708,7 +3708,7 @@
         <v>60</v>
       </c>
       <c r="Y13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
         <v>22</v>
@@ -3717,13 +3717,13 @@
         <v>25</v>
       </c>
       <c r="AB13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC13" t="n">
         <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE13" t="n">
         <v>18.5</v>
@@ -3852,7 +3852,7 @@
         <v>5.7</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
         <v>11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M14" t="n">
         <v>1.13</v>
@@ -3938,7 +3938,7 @@
         <v>1.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R14" t="n">
         <v>1.17</v>
@@ -3980,7 +3980,7 @@
         <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
@@ -4004,13 +4004,13 @@
         <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN14" t="n">
         <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AP14" t="n">
         <v>7.4</v>
@@ -4031,7 +4031,7 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
         <v>11.5</v>
@@ -4064,71 +4064,71 @@
         <v>21</v>
       </c>
       <c r="BG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS14" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BN14" t="n">
+      <c r="BT14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU14" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BT14" t="n">
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
         <v>13</v>
       </c>
-      <c r="BU14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.61</v>
-      </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.64</v>
+        <v>13.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 01:03:03</t>
+          <t>2026-06-24 03:11:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
         <v>9.6</v>
@@ -3840,7 +3840,7 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3852,19 +3852,19 @@
         <v>5.7</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV13" t="n">
         <v>11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 03:11:32</t>
+          <t>2026-06-24 05:20:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -905,11 +905,11 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.02</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1138,19 +1138,19 @@
         <v>1.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
         <v>1.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,28 +1356,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SK Super Nova</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Sindri</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,28 +1389,28 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="P4" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1581,21 +1581,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,28 +1610,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>SK Super Nova</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,34 +1643,34 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1835,14 +1835,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1906,13 +1906,13 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,28 +2405,28 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,34 +2659,34 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2916,31 +2916,31 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
         <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,34 +3167,34 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,28 +3421,28 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,498 +3637,752 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.3</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>7.8</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
-        <v>2.06</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1.76</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>2.98</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
         <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
         <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 05:20:00</t>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-24 07:28:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Londrina</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.95</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>5.5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>6.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>3.15</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>3.55</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>1.59</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>1.13</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N15" t="n">
         <v>2.48</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O15" t="n">
         <v>1.58</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P15" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q15" t="n">
         <v>2.72</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>1.17</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>5.9</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>2.36</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>1.63</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V15" t="n">
         <v>1.19</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W15" t="n">
         <v>2.06</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X15" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y15" t="n">
         <v>14</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z15" t="n">
         <v>46</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA15" t="n">
         <v>250</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB15" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC15" t="n">
         <v>8</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD15" t="n">
         <v>26</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE15" t="n">
         <v>150</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AF15" t="n">
         <v>10</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AG15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AH15" t="n">
         <v>950</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AI15" t="n">
         <v>180</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AJ15" t="n">
         <v>23</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK15" t="n">
         <v>29</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AL15" t="n">
         <v>70</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AM15" t="n">
         <v>320</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AN15" t="n">
         <v>25</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AO15" t="n">
         <v>290</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AP15" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AQ15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AR15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AT15" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AU15" t="n">
         <v>7</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AV15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AW15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AX15" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AY15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="AZ15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BA15" t="n">
         <v>11.5</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB15" t="n">
         <v>19.5</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BC15" t="n">
         <v>8.6</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BD15" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BE15" t="n">
         <v>12</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BF15" t="n">
         <v>21</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BG15" t="n">
         <v>12</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BH15" t="n">
         <v>2.66</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BI15" t="n">
         <v>2.44</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BJ15" t="n">
         <v>13</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BK15" t="n">
         <v>7.2</v>
       </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
         <v>15</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BN15" t="n">
         <v>4.2</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BO15" t="n">
         <v>3.75</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BP15" t="n">
         <v>15.5</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BQ15" t="n">
         <v>7.8</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="BR15" t="n">
         <v>44</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="BS15" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="BT15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="BU15" t="n">
         <v>5.8</v>
       </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
         <v>13</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>13.5</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
         <v>11.5</v>
       </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-24 05:20:00</t>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-24 07:28:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,94 +857,94 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>1.26</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -962,7 +962,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP2" t="n">
         <v>1.03</v>
@@ -1016,71 +1016,71 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1111,112 +1111,112 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>1.46</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AP3" t="n">
         <v>1.03</v>
@@ -1270,61 +1270,61 @@
         <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.04</v>
@@ -1401,7 +1401,7 @@
         <v>1.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
         <v>1.04</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
         <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.35</v>
+        <v>2.32</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
         <v>3.6</v>
@@ -1649,82 +1649,82 @@
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
@@ -1775,64 +1775,64 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2127,112 +2127,112 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="J7" t="n">
         <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>1.03</v>
@@ -2286,7 +2286,7 @@
         <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
         <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,7 +2429,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
         <v>2.98</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3176,13 +3176,13 @@
         <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
@@ -3415,7 +3415,7 @@
         <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3436,7 +3436,7 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -3454,34 +3454,34 @@
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -3562,55 +3562,55 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3651,112 +3651,112 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.47</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
         <v>1.03</v>
@@ -3807,74 +3807,74 @@
         <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>1.63</v>
       </c>
       <c r="I14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
@@ -3941,7 +3941,7 @@
         <v>1.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S14" t="n">
         <v>1.76</v>
@@ -3953,7 +3953,7 @@
         <v>2.98</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W14" t="n">
         <v>1.24</v>
@@ -4076,7 +4076,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4085,10 +4085,10 @@
         <v>8.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4100,19 +4100,19 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
         <v>5.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>
@@ -4201,10 +4201,10 @@
         <v>5.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V15" t="n">
         <v>1.19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 07:28:39</t>
+          <t>2026-06-24 09:37:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H2" t="n">
         <v>1.62</v>
       </c>
       <c r="I2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W2" t="n">
         <v>1.17</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
         <v>55</v>
@@ -962,125 +962,125 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>13</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="H3" t="n">
         <v>1.37</v>
       </c>
       <c r="I3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="K3" t="n">
         <v>6.2</v>
@@ -1144,34 +1144,34 @@
         <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T3" t="n">
         <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
         <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
         <v>15.5</v>
@@ -1189,7 +1189,7 @@
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG3" t="n">
         <v>34</v>
@@ -1216,73 +1216,73 @@
         <v>130</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
         <v>4.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,37 +1294,37 @@
         <v>12.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BV3" t="n">
         <v>8.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BX3" t="n">
         <v>21</v>
       </c>
       <c r="BY3" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="S4" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1425,34 +1425,34 @@
         <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1461,16 +1461,16 @@
         <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
@@ -1488,7 +1488,7 @@
         <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>1.01</v>
@@ -1497,16 +1497,16 @@
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
@@ -1515,80 +1515,80 @@
         <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE4" t="n">
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM4" t="n">
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO4" t="n">
         <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>3.6</v>
@@ -1649,34 +1649,34 @@
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>25</v>
@@ -1691,10 +1691,10 @@
         <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
@@ -1727,58 +1727,58 @@
         <v>36</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>16.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.6</v>
@@ -1790,7 +1790,7 @@
         <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,37 +1802,37 @@
         <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
         <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.48</v>
+        <v>4.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2130,76 +2130,76 @@
         <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
         <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
         <v>30</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>32</v>
@@ -2208,7 +2208,7 @@
         <v>44</v>
       </c>
       <c r="AG7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
         <v>28</v>
@@ -2235,122 +2235,122 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>15.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
         <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.56</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -2889,166 +2889,166 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -3143,166 +3143,166 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>10.5</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>4.4</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -3397,100 +3397,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>2.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P12" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -3499,43 +3499,43 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
@@ -3544,7 +3544,7 @@
         <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
         <v>1.03</v>
@@ -3559,7 +3559,7 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI12" t="n">
         <v>2.14</v>
@@ -3568,13 +3568,13 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
@@ -3586,41 +3586,41 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>20</v>
+        <v>1.06</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>20</v>
+        <v>1.06</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
         <v>2.7</v>
@@ -3690,7 +3690,7 @@
         <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
         <v>2.04</v>
@@ -3702,7 +3702,7 @@
         <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
         <v>9.199999999999999</v>
@@ -3720,7 +3720,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
@@ -3729,7 +3729,7 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
         <v>16</v>
@@ -3738,7 +3738,7 @@
         <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
         <v>65</v>
@@ -3753,64 +3753,64 @@
         <v>230</v>
       </c>
       <c r="AN13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="n">
         <v>2.78</v>
@@ -3822,59 +3822,59 @@
         <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BN13" t="n">
         <v>6.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP13" t="n">
         <v>32</v>
       </c>
       <c r="BQ13" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
         <v>60</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV13" t="n">
         <v>32</v>
       </c>
       <c r="BW13" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BX13" t="n">
         <v>60</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>65</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>1.63</v>
       </c>
       <c r="I14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
@@ -4082,10 +4082,10 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO14" t="n">
         <v>4.9</v>
@@ -4094,7 +4094,7 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4112,7 +4112,7 @@
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
         <v>1.95</v>
@@ -4174,7 +4174,7 @@
         <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.59</v>
@@ -4201,7 +4201,7 @@
         <v>5.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN15" t="n">
         <v>4.2</v>
@@ -4348,10 +4348,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
         <v>11.5</v>
@@ -4360,7 +4360,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4372,17 +4372,17 @@
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 09:37:19</t>
+          <t>2026-06-24 11:45:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -899,22 +899,22 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
         <v>970</v>
@@ -923,7 +923,7 @@
         <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -935,152 +935,152 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH2" t="n">
         <v>25</v>
       </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO2" t="n">
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH2" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1111,100 +1111,100 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>7.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH3" t="n">
         <v>32</v>
       </c>
-      <c r="Y3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>34</v>
       </c>
-      <c r="AH3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="AK3" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AL3" t="n">
         <v>110</v>
@@ -1213,118 +1213,118 @@
         <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BO3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BW3" t="n">
         <v>5.5</v>
       </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BX3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.13</v>
@@ -1392,37 +1392,37 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="n">
         <v>85</v>
@@ -1431,13 +1431,13 @@
         <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
         <v>22</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1455,16 +1455,16 @@
         <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN4" t="n">
         <v>3.9</v>
@@ -1488,7 +1488,7 @@
         <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
         <v>1.01</v>
@@ -1497,16 +1497,16 @@
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
@@ -1515,7 +1515,7 @@
         <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
         <v>1.01</v>
@@ -1524,7 +1524,7 @@
         <v>2.88</v>
       </c>
       <c r="BG4" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
         <v>8.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.48</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
@@ -1643,13 +1643,13 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
         <v>1.89</v>
@@ -1658,25 +1658,25 @@
         <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
         <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
         <v>25</v>
@@ -1691,10 +1691,10 @@
         <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
@@ -1709,76 +1709,76 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
         <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR5" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW5" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AX5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>3.5</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BA5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BF5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.6</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -1888,22 +1888,22 @@
         <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.06</v>
@@ -1927,10 +1927,10 @@
         <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1939,10 +1939,10 @@
         <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1963,7 +1963,7 @@
         <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="n">
         <v>60</v>
@@ -1981,7 +1981,7 @@
         <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
         <v>3.45</v>
@@ -1990,13 +1990,13 @@
         <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
         <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV6" t="n">
         <v>4.1</v>
@@ -2029,7 +2029,7 @@
         <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG6" t="n">
         <v>5.2</v>
@@ -2056,7 +2056,7 @@
         <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2127,82 +2127,82 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
         <v>30</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
         <v>44</v>
@@ -2211,146 +2211,146 @@
         <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN7" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.88</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BB7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.23</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
         <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
         <v>3.65</v>
@@ -2420,7 +2420,7 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.04</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.2</v>
+        <v>2.08</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
@@ -2576,7 +2576,7 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.4</v>
+        <v>2.02</v>
       </c>
       <c r="BT8" t="n">
         <v>8.4</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>2.02</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.8</v>
+        <v>2.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.4</v>
+        <v>2.02</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2635,64 +2635,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
         <v>22</v>
@@ -2701,10 +2701,10 @@
         <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
         <v>17</v>
@@ -2713,152 +2713,152 @@
         <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>95</v>
       </c>
       <c r="AJ9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN9" t="n">
         <v>70</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>75</v>
       </c>
       <c r="AO9" t="n">
         <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="n">
         <v>2.66</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.06</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>6.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>2</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>2</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
         <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
         <v>32</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2964,116 +2964,116 @@
         <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
         <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BO10" t="n">
         <v>3.85</v>
       </c>
-      <c r="AY10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
@@ -3087,10 +3087,10 @@
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
         <v>3.1</v>
@@ -3155,22 +3155,22 @@
         <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
         <v>1.56</v>
@@ -3182,127 +3182,127 @@
         <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
         <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
         <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
         <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO11" t="n">
         <v>70</v>
       </c>
       <c r="AP11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>7</v>
       </c>
-      <c r="BC11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
         <v>2.76</v>
@@ -3421,7 +3421,7 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
         <v>1.56</v>
@@ -3430,25 +3430,25 @@
         <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="T12" t="n">
         <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -3466,7 +3466,7 @@
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
@@ -3481,10 +3481,10 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="n">
         <v>70</v>
@@ -3493,7 +3493,7 @@
         <v>60</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -3508,22 +3508,22 @@
         <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
         <v>1.01</v>
@@ -3541,7 +3541,7 @@
         <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
         <v>1.01</v>
@@ -3559,7 +3559,7 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="BI12" t="n">
         <v>2.14</v>
@@ -3574,28 +3574,28 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.19</v>
+        <v>1.78</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BU12" t="n">
         <v>3.7</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.06</v>
+        <v>1.79</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
@@ -3672,10 +3672,10 @@
         <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
         <v>1.53</v>
@@ -3684,13 +3684,13 @@
         <v>1.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
         <v>2.04</v>
@@ -3711,34 +3711,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
         <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
         <v>65</v>
@@ -3747,7 +3747,7 @@
         <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM13" t="n">
         <v>230</v>
@@ -3756,61 +3756,61 @@
         <v>70</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AZ13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB13" t="n">
         <v>5</v>
       </c>
-      <c r="BA13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="n">
         <v>2.78</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G14" t="n">
         <v>5.1</v>
@@ -3914,7 +3914,7 @@
         <v>1.63</v>
       </c>
       <c r="I14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
@@ -3929,58 +3929,58 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R14" t="n">
         <v>2.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
         <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF14" t="n">
         <v>60</v>
@@ -3989,7 +3989,7 @@
         <v>26</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>25</v>
@@ -4001,28 +4001,28 @@
         <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AP14" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
         <v>1.03</v>
@@ -4034,7 +4034,7 @@
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX14" t="n">
         <v>1.01</v>
@@ -4061,55 +4061,55 @@
         <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BH14" t="n">
         <v>6.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN14" t="n">
         <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT14" t="n">
         <v>5.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BW14" t="n">
         <v>5.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H15" t="n">
         <v>5.5</v>
@@ -4171,10 +4171,10 @@
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
         <v>1.59</v>
@@ -4183,37 +4183,37 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P15" t="n">
         <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X15" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
         <v>14</v>
@@ -4228,19 +4228,19 @@
         <v>5.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -4249,79 +4249,79 @@
         <v>180</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="n">
         <v>320</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>290</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT15" t="n">
         <v>5.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BI15" t="n">
         <v>2.44</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN15" t="n">
         <v>4.2</v>
@@ -4345,10 +4345,10 @@
         <v>3.75</v>
       </c>
       <c r="BP15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4360,7 +4360,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4372,17 +4372,17 @@
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 11:45:30</t>
+          <t>2026-06-24 13:53:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,28 +857,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -896,7 +896,7 @@
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -905,10 +905,10 @@
         <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -965,10 +965,10 @@
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
         <v>7.6</v>
@@ -995,7 +995,7 @@
         <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
         <v>4.5</v>
@@ -1016,13 +1016,13 @@
         <v>4.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1111,175 +1111,175 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="n">
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD3" t="n">
         <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF3" t="n">
         <v>130</v>
       </c>
       <c r="AG3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AH3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI3" t="n">
         <v>32</v>
       </c>
-      <c r="AI3" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AK3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AL3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="n">
         <v>110</v>
       </c>
-      <c r="AM3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>140</v>
-      </c>
       <c r="AO3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>18.5</v>
       </c>
       <c r="BB3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
         <v>5.9</v>
@@ -1288,40 +1288,40 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
         <v>13.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>10</v>
-      </c>
       <c r="BT3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BV3" t="n">
         <v>7.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY3" t="n">
         <v>7.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
         <v>4.5</v>
@@ -1377,10 +1377,10 @@
         <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.13</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
         <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T4" t="n">
         <v>1.36</v>
@@ -1413,19 +1413,19 @@
         <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
         <v>85</v>
       </c>
       <c r="Y4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Z4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
         <v>150</v>
@@ -1434,10 +1434,10 @@
         <v>32</v>
       </c>
       <c r="AC4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1470,7 +1470,7 @@
         <v>3.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
@@ -1485,10 +1485,10 @@
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
         <v>1.01</v>
@@ -1497,37 +1497,37 @@
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC4" t="n">
         <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE4" t="n">
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
@@ -1581,14 +1581,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1619,208 +1619,208 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI5" t="n">
         <v>2.86</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X5" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.76</v>
-      </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT5" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BU5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
         <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
         <v>2.26</v>
@@ -1903,16 +1903,16 @@
         <v>1.53</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
         <v>2.06</v>
@@ -1927,10 +1927,10 @@
         <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1939,7 +1939,7 @@
         <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2145,7 +2145,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2232,7 +2232,7 @@
         <v>130</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>8</v>
@@ -2253,7 +2253,7 @@
         <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
         <v>17.5</v>
@@ -2277,7 +2277,7 @@
         <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
         <v>4.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
         <v>5.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -2650,10 +2650,10 @@
         <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
@@ -2668,7 +2668,7 @@
         <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
@@ -2686,7 +2686,7 @@
         <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
         <v>9</v>
@@ -2737,7 +2737,7 @@
         <v>240</v>
       </c>
       <c r="AN9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO9" t="n">
         <v>75</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
         <v>14</v>
@@ -2779,7 +2779,7 @@
         <v>5.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC9" t="n">
         <v>5.5</v>
@@ -2788,7 +2788,7 @@
         <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
         <v>5.6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -2892,28 +2892,28 @@
         <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I10" t="n">
         <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O10" t="n">
         <v>1.49</v>
@@ -2940,7 +2940,7 @@
         <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X10" t="n">
         <v>11</v>
@@ -2976,13 +2976,13 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
         <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
@@ -3021,7 +3021,7 @@
         <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
@@ -3054,19 +3054,19 @@
         <v>2.84</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.9</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
         <v>7.2</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -3176,13 +3176,13 @@
         <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
@@ -3191,7 +3191,7 @@
         <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
@@ -3200,34 +3200,34 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
         <v>75</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>85</v>
@@ -3236,16 +3236,16 @@
         <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
         <v>70</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -3421,7 +3421,7 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="O12" t="n">
         <v>1.56</v>
@@ -3430,25 +3430,25 @@
         <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2</v>
+        <v>1.06</v>
       </c>
       <c r="T12" t="n">
         <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -3508,7 +3508,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
         <v>1.01</v>
@@ -3520,7 +3520,7 @@
         <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
         <v>1.03</v>
@@ -3577,7 +3577,7 @@
         <v>1.78</v>
       </c>
       <c r="BN12" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="BO12" t="n">
         <v>3.7</v>
@@ -3595,7 +3595,7 @@
         <v>1.74</v>
       </c>
       <c r="BT12" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="BU12" t="n">
         <v>3.7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
         <v>2.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J13" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
@@ -3681,31 +3681,31 @@
         <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
         <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y13" t="n">
         <v>9.199999999999999</v>
@@ -3714,19 +3714,19 @@
         <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>16.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF13" t="n">
         <v>22</v>
@@ -3735,88 +3735,88 @@
         <v>16.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN13" t="n">
         <v>65</v>
       </c>
-      <c r="AK13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>70</v>
-      </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX13" t="n">
         <v>5</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AY13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="n">
         <v>2.78</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>4.2</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
         <v>5.7</v>
@@ -3953,10 +3953,10 @@
         <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
         <v>65</v>
@@ -4064,7 +4064,7 @@
         <v>15.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="n">
         <v>6.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I15" t="n">
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.55</v>
@@ -4183,7 +4183,7 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
         <v>1.56</v>
@@ -4192,10 +4192,10 @@
         <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
         <v>5.7</v>
@@ -4210,7 +4210,7 @@
         <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X15" t="n">
         <v>10.5</v>
@@ -4273,7 +4273,7 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="AS15" t="n">
         <v>7.8</v>
@@ -4330,7 +4330,7 @@
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4342,13 +4342,13 @@
         <v>4.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP15" t="n">
         <v>15</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4357,16 +4357,16 @@
         <v>11.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 13:53:57</t>
+          <t>2026-06-24 16:03:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,28 +857,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -887,34 +887,34 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z2" t="n">
         <v>970</v>
@@ -929,7 +929,7 @@
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>970</v>
@@ -962,10 +962,10 @@
         <v>130</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
         <v>6.8</v>
@@ -974,49 +974,49 @@
         <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV2" t="n">
         <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1052,10 +1052,10 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU2" t="n">
         <v>3.4</v>
@@ -1064,13 +1064,13 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="J3" t="n">
         <v>6.6</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.16</v>
@@ -1144,7 +1144,7 @@
         <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R3" t="n">
         <v>2.04</v>
@@ -1159,13 +1159,13 @@
         <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="W3" t="n">
         <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1177,10 +1177,10 @@
         <v>15</v>
       </c>
       <c r="AB3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AC3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="n">
         <v>14.5</v>
@@ -1189,37 +1189,37 @@
         <v>16.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AG3" t="n">
         <v>46</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AK3" t="n">
         <v>140</v>
       </c>
       <c r="AL3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN3" t="n">
         <v>100</v>
       </c>
-      <c r="AM3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>110</v>
-      </c>
       <c r="AO3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
@@ -1231,7 +1231,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU3" t="n">
         <v>13</v>
@@ -1243,10 +1243,10 @@
         <v>9.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>17.5</v>
@@ -1255,76 +1255,76 @@
         <v>18.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
         <v>2.96</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
         <v>13.5</v>
       </c>
       <c r="BO3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>10</v>
       </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>11</v>
-      </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU3" t="n">
         <v>4</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX3" t="n">
         <v>17</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
         <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,25 +1506,25 @@
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
         <v>2.92</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="n">
         <v>8.199999999999999</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
         <v>2.66</v>
@@ -1634,10 +1634,10 @@
         <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1646,31 +1646,31 @@
         <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
         <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
         <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
@@ -1682,7 +1682,7 @@
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
@@ -1733,7 +1733,7 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
         <v>5.9</v>
@@ -1745,10 +1745,10 @@
         <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX5" t="n">
         <v>19</v>
@@ -1757,25 +1757,25 @@
         <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
         <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
         <v>5.5</v>
@@ -1784,7 +1784,7 @@
         <v>3.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.6</v>
       </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.64</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,188 +1915,188 @@
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.93</v>
@@ -2175,7 +2175,7 @@
         <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
         <v>1.24</v>
@@ -2292,7 +2292,7 @@
         <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.02</v>
+        <v>6.4</v>
       </c>
       <c r="BT8" t="n">
         <v>8.4</v>
@@ -2588,7 +2588,7 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2600,11 +2600,11 @@
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.02</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.54</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
         <v>2.7</v>
@@ -3155,10 +3155,10 @@
         <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.88</v>
       </c>
       <c r="I12" t="n">
         <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3421,10 +3421,10 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
         <v>1.46</v>
@@ -3439,16 +3439,16 @@
         <v>1.06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -3481,7 +3481,7 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>95</v>
@@ -3499,64 +3499,64 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO12" t="n">
         <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="n">
         <v>2.7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3651,175 +3651,175 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.72</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.32</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM13" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU13" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AV13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>34</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BJ13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK13" t="n">
         <v>4.7</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BQ13" t="n">
         <v>6</v>
       </c>
       <c r="BR13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW13" t="n">
         <v>6</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I14" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.16</v>
@@ -3929,142 +3929,142 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="R14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="T14" t="n">
         <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X14" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AB14" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AC14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
         <v>18</v>
       </c>
-      <c r="AD14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>19</v>
-      </c>
       <c r="AF14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL14" t="n">
         <v>60</v>
       </c>
-      <c r="AG14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
       <c r="AM14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AO14" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AU14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BF14" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="n">
         <v>6.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H15" t="n">
         <v>5.7</v>
@@ -4174,7 +4174,7 @@
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.59</v>
@@ -4201,10 +4201,10 @@
         <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
         <v>1.18</v>
@@ -4225,7 +4225,7 @@
         <v>250</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -4240,7 +4240,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -4276,10 +4276,10 @@
         <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU15" t="n">
         <v>7.2</v>
@@ -4288,7 +4288,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
         <v>8.4</v>
@@ -4297,28 +4297,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
         <v>18.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="n">
         <v>2.68</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 16:03:17</t>
+          <t>2026-06-24 18:13:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
@@ -884,7 +884,7 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.06</v>
@@ -896,76 +896,76 @@
         <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="AG2" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="AL2" t="n">
         <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>130</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>6.8</v>
@@ -974,46 +974,46 @@
         <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
         <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BG2" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.16</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1.11</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R3" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
         <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
         <v>60</v>
@@ -1177,22 +1177,22 @@
         <v>15</v>
       </c>
       <c r="AB3" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AC3" t="n">
         <v>21</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
         <v>16.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
@@ -1201,25 +1201,25 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM3" t="n">
         <v>320</v>
       </c>
-      <c r="AK3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>95</v>
-      </c>
       <c r="AN3" t="n">
-        <v>100</v>
+        <v>530</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
@@ -1231,46 +1231,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
         <v>13</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>9.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
         <v>18.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="n">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         <v>4.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BV3" t="n">
         <v>7.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         <v>1.36</v>
       </c>
       <c r="U4" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.2</v>
@@ -1425,64 +1425,64 @@
         <v>60</v>
       </c>
       <c r="Z4" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA4" t="n">
         <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC4" t="n">
         <v>21</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM4" t="n">
         <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AO4" t="n">
         <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,89 +1506,89 @@
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>2.92</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1649,13 +1649,13 @@
         <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
         <v>2.06</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
         <v>3.85</v>
@@ -1664,67 +1664,67 @@
         <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
         <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF5" t="n">
         <v>38</v>
       </c>
-      <c r="AB5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>28</v>
-      </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AM5" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AO5" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1733,22 +1733,22 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>19</v>
@@ -1757,28 +1757,28 @@
         <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="n">
         <v>3.35</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
         <v>2.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1921,118 +1921,118 @@
         <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.03</v>
+        <v>1.93</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -2166,16 +2166,16 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W7" t="n">
         <v>1.24</v>
@@ -2190,10 +2190,10 @@
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
         <v>9.199999999999999</v>
@@ -2202,10 +2202,10 @@
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AG7" t="n">
         <v>24</v>
@@ -2214,79 +2214,79 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>90</v>
+        <v>470</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="AM7" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR7" t="n">
         <v>5.6</v>
       </c>
-      <c r="AR7" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AS7" t="n">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AV7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>17.5</v>
+        <v>3.95</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
         <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
         <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2390,13 +2390,13 @@
         <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J8" t="n">
         <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.49</v>
@@ -2429,55 +2429,55 @@
         <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
         <v>1.75</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2489,58 +2489,58 @@
         <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB8" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BC8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH8" t="n">
         <v>2.94</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.82</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
         <v>2.92</v>
@@ -2659,79 +2659,79 @@
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
         <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
         <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>60</v>
       </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>65</v>
-      </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
         <v>240</v>
@@ -2743,58 +2743,58 @@
         <v>75</v>
       </c>
       <c r="AP9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU9" t="n">
         <v>6</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="n">
         <v>2.66</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
         <v>3.85</v>
@@ -2901,10 +2901,10 @@
         <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.54</v>
@@ -2949,10 +2949,10 @@
         <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>7.6</v>
@@ -2964,10 +2964,10 @@
         <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
@@ -2976,16 +2976,16 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>85</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>38</v>
-      </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM10" t="n">
         <v>200</v>
@@ -3006,10 +3006,10 @@
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6.4</v>
@@ -3018,37 +3018,37 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5.8</v>
       </c>
-      <c r="BF10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH10" t="n">
         <v>2.84</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3197,19 +3197,19 @@
         <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
@@ -3218,91 +3218,91 @@
         <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="AM11" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="AP11" t="n">
         <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV11" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AW11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AX11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY11" t="n">
         <v>5</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AZ11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD11" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.78</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3421,37 +3421,37 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.06</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
         <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -3460,19 +3460,19 @@
         <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
         <v>970</v>
@@ -3481,82 +3481,82 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.88</v>
+        <v>5.7</v>
       </c>
       <c r="AS12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT12" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AU12" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.88</v>
+        <v>5.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.72</v>
+        <v>5.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.95</v>
+        <v>5.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.04</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.04</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.06</v>
+        <v>2.92</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="n">
         <v>2.7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
         <v>2.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.51</v>
@@ -3678,7 +3678,7 @@
         <v>2.72</v>
       </c>
       <c r="O13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
         <v>1.54</v>
@@ -3717,7 +3717,7 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>7.8</v>
@@ -3750,7 +3750,7 @@
         <v>70</v>
       </c>
       <c r="AM13" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>55</v>
@@ -3768,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3777,37 +3777,37 @@
         <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
         <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
         <v>34</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>4.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.16</v>
@@ -3935,10 +3935,10 @@
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R14" t="n">
         <v>2.12</v>
@@ -3950,40 +3950,40 @@
         <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>290</v>
+        <v>110</v>
       </c>
       <c r="Y14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
         <v>30</v>
       </c>
       <c r="AB14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AC14" t="n">
         <v>14.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AG14" t="n">
         <v>25</v>
@@ -3995,67 +3995,67 @@
         <v>21</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AK14" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
         <v>28</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU14" t="n">
         <v>11</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE14" t="n">
         <v>24</v>
@@ -4064,7 +4064,7 @@
         <v>18.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="n">
         <v>6.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 18:13:46</t>
+          <t>2026-06-24 20:24:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -866,25 +866,25 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.06</v>
@@ -902,7 +902,7 @@
         <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>2.54</v>
@@ -923,7 +923,7 @@
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
         <v>19</v>
@@ -935,28 +935,28 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AK2" t="n">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AL2" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN2" t="n">
         <v>130</v>
@@ -980,7 +980,7 @@
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV2" t="n">
         <v>7.8</v>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
@@ -998,7 +998,7 @@
         <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>4.2</v>
@@ -1010,7 +1010,7 @@
         <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BF2" t="n">
         <v>4.2</v>
@@ -1019,22 +1019,22 @@
         <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,41 +1046,41 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="BT2" t="n">
         <v>4.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -1114,61 +1114,61 @@
         <v>8.4</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K3" t="n">
         <v>6.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
         <v>15</v>
@@ -1180,10 +1180,10 @@
         <v>290</v>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
         <v>16.5</v>
@@ -1192,7 +1192,7 @@
         <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
@@ -1201,7 +1201,7 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AK3" t="n">
         <v>130</v>
@@ -1216,13 +1216,13 @@
         <v>530</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>9.199999999999999</v>
@@ -1231,19 +1231,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
         <v>13</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>16</v>
@@ -1255,28 +1255,28 @@
         <v>18.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
         <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
@@ -1288,10 +1288,10 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BO3" t="n">
         <v>9.6</v>
@@ -1300,31 +1300,31 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BT3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BV3" t="n">
         <v>7.6</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
         <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>6.6</v>
@@ -1398,19 +1398,19 @@
         <v>4.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
         <v>1.2</v>
@@ -1422,13 +1422,13 @@
         <v>85</v>
       </c>
       <c r="Y4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z4" t="n">
         <v>170</v>
       </c>
       <c r="AA4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
         <v>29</v>
@@ -1437,7 +1437,7 @@
         <v>21</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
@@ -1449,7 +1449,7 @@
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>40</v>
@@ -1473,16 +1473,16 @@
         <v>26</v>
       </c>
       <c r="AP4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,25 +1506,25 @@
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH4" t="n">
         <v>8</v>
@@ -1533,7 +1533,7 @@
         <v>6.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
         <v>4.4</v>
@@ -1542,7 +1542,7 @@
         <v>48</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
@@ -1554,13 +1554,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR4" t="n">
         <v>15</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT4" t="n">
         <v>11.5</v>
@@ -1578,17 +1578,17 @@
         <v>28</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>7.2</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
@@ -1649,7 +1649,7 @@
         <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
         <v>2.06</v>
@@ -1658,13 +1658,13 @@
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
         <v>1.6</v>
@@ -1715,16 +1715,16 @@
         <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1766,7 +1766,7 @@
         <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
         <v>7.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I6" t="n">
         <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>1.5</v>
@@ -1900,13 +1900,13 @@
         <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1924,7 +1924,7 @@
         <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -2008,22 +2008,22 @@
         <v>4.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.34</v>
+        <v>2.5</v>
       </c>
       <c r="BB6" t="n">
         <v>1.34</v>
       </c>
       <c r="BC6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD6" t="n">
         <v>2.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.34</v>
       </c>
       <c r="BE6" t="n">
         <v>1.34</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
         <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2166,7 +2166,7 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
@@ -2175,13 +2175,13 @@
         <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
         <v>9</v>
@@ -2190,13 +2190,13 @@
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
@@ -2229,13 +2229,13 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -2244,7 +2244,7 @@
         <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -2256,34 +2256,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG7" t="n">
         <v>4.9</v>
@@ -2295,7 +2295,7 @@
         <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
         <v>6.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
         <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2456,7 +2456,7 @@
         <v>38</v>
       </c>
       <c r="AE8" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
@@ -2465,10 +2465,10 @@
         <v>21</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
@@ -2477,28 +2477,28 @@
         <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR8" t="n">
         <v>5.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
         <v>3.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
         <v>2.92</v>
@@ -2647,7 +2647,7 @@
         <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2659,16 +2659,16 @@
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
@@ -2680,13 +2680,13 @@
         <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
         <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
         <v>8.199999999999999</v>
@@ -2719,7 +2719,7 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>190</v>
@@ -2731,10 +2731,10 @@
         <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>200</v>
+        <v>460</v>
       </c>
       <c r="AM9" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
         <v>65</v>
@@ -2779,22 +2779,22 @@
         <v>8</v>
       </c>
       <c r="BB9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC9" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
         <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
         <v>2.66</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -2892,49 +2892,49 @@
         <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
         <v>3.85</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
         <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2943,7 +2943,7 @@
         <v>1.73</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
         <v>13</v>
@@ -2967,7 +2967,7 @@
         <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
@@ -2976,40 +2976,40 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
         <v>75</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
         <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6.4</v>
@@ -3018,55 +3018,55 @@
         <v>13</v>
       </c>
       <c r="AW10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BC10" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BD10" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>6</v>
       </c>
-      <c r="BF10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH10" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>4.9</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -3209,7 +3209,7 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
@@ -3218,10 +3218,10 @@
         <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3230,7 +3230,7 @@
         <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
@@ -3242,16 +3242,16 @@
         <v>450</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>110</v>
       </c>
       <c r="AO11" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.1</v>
@@ -3260,7 +3260,7 @@
         <v>5.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
         <v>4.9</v>
@@ -3269,34 +3269,34 @@
         <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD11" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
         <v>7.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
         <v>3.3</v>
@@ -3418,19 +3418,19 @@
         <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.52</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -3439,10 +3439,10 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
         <v>1.43</v>
@@ -3466,7 +3466,7 @@
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
@@ -3511,10 +3511,10 @@
         <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
@@ -3526,34 +3526,34 @@
         <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BF12" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7</v>
       </c>
       <c r="BG12" t="n">
         <v>8.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
         <v>29</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
         <v>30</v>
@@ -4025,7 +4025,7 @@
         <v>15.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU14" t="n">
         <v>11</v>
@@ -4046,13 +4046,13 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB14" t="n">
         <v>40</v>
       </c>
       <c r="BC14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD14" t="n">
         <v>22</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O15" t="n">
         <v>1.56</v>
@@ -4201,13 +4201,13 @@
         <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U15" t="n">
         <v>1.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
         <v>2.12</v>
@@ -4237,7 +4237,7 @@
         <v>160</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
@@ -4249,7 +4249,7 @@
         <v>180</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK15" t="n">
         <v>28</v>
@@ -4273,22 +4273,22 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT15" t="n">
         <v>5.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX15" t="n">
         <v>8.4</v>
@@ -4297,46 +4297,46 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC15" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BD15" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7</v>
-      </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="n">
         <v>2.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN15" t="n">
         <v>4.2</v>
@@ -4348,7 +4348,7 @@
         <v>15</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4357,7 +4357,7 @@
         <v>11.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU15" t="n">
         <v>5.9</v>
@@ -4366,13 +4366,13 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 20:24:08</t>
+          <t>2026-06-24 22:34:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
@@ -878,7 +878,7 @@
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -893,58 +893,58 @@
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>180</v>
+        <v>16.5</v>
       </c>
       <c r="AB2" t="n">
         <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
         <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>700</v>
@@ -959,61 +959,61 @@
         <v>700</v>
       </c>
       <c r="AN2" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.84</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
         <v>6.8</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,31 +1046,31 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="BT2" t="n">
         <v>4.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>6.8</v>
@@ -1141,37 +1141,37 @@
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
         <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="Y3" t="n">
         <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA3" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
         <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>16.5</v>
@@ -1192,7 +1192,7 @@
         <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
@@ -1201,10 +1201,10 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AK3" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AL3" t="n">
         <v>390</v>
@@ -1216,10 +1216,10 @@
         <v>530</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -1228,10 +1228,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="AU3" t="n">
         <v>13</v>
@@ -1240,79 +1240,79 @@
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>11</v>
       </c>
-      <c r="BN3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>10</v>
-      </c>
       <c r="BT3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV3" t="n">
         <v>7.6</v>
@@ -1324,7 +1324,7 @@
         <v>970</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
         <v>6.6</v>
@@ -1389,37 +1389,37 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O4" t="n">
         <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X4" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="Y4" t="n">
         <v>55</v>
@@ -1431,7 +1431,7 @@
         <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
         <v>21</v>
@@ -1446,16 +1446,16 @@
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1467,22 +1467,22 @@
         <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
@@ -1491,10 +1491,10 @@
         <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1506,52 +1506,52 @@
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
         <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="BH4" t="n">
         <v>8</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL4" t="n">
         <v>48</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO4" t="n">
         <v>4.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ4" t="n">
         <v>4.6</v>
@@ -1560,35 +1560,35 @@
         <v>15</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT4" t="n">
         <v>11.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>34</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>28</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>7.2</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
         <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
@@ -1661,16 +1661,16 @@
         <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
@@ -1679,7 +1679,7 @@
         <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1748,10 +1748,10 @@
         <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="AY5" t="n">
         <v>12.5</v>
@@ -1766,16 +1766,16 @@
         <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
         <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG5" t="n">
         <v>6.8</v>
@@ -1787,37 +1787,37 @@
         <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU5" t="n">
         <v>4.2</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
         <v>2.54</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Q6" t="n">
         <v>2.66</v>
@@ -1912,19 +1912,19 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
         <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1951,7 +1951,7 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
         <v>970</v>
@@ -2005,31 +2005,31 @@
         <v>1.34</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>1.32</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="BB6" t="n">
         <v>1.34</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.9</v>
+        <v>1.34</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="BE6" t="n">
         <v>1.34</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
         <v>1.55</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="n">
         <v>2.1</v>
@@ -2154,10 +2154,10 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
         <v>2.26</v>
@@ -2169,22 +2169,22 @@
         <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
         <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
         <v>14</v>
@@ -2211,7 +2211,7 @@
         <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>290</v>
@@ -2235,7 +2235,7 @@
         <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -2244,7 +2244,7 @@
         <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -2256,34 +2256,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
         <v>4.9</v>
@@ -2295,10 +2295,10 @@
         <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,19 +2310,19 @@
         <v>8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BT7" t="n">
         <v>4.6</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
         <v>2.42</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,10 +2447,10 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
         <v>38</v>
@@ -2489,122 +2489,122 @@
         <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AV8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.8</v>
       </c>
-      <c r="AW8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BO8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>2.08</v>
       </c>
-      <c r="BN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BT8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.6</v>
+        <v>2.08</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.4</v>
+        <v>2.08</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2653,31 +2653,31 @@
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.58</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.56</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
         <v>1.73</v>
@@ -2689,10 +2689,10 @@
         <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z9" t="n">
         <v>19.5</v>
@@ -2704,7 +2704,7 @@
         <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
         <v>15.5</v>
@@ -2752,7 +2752,7 @@
         <v>15.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2764,7 +2764,7 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>15</v>
@@ -2776,37 +2776,37 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF9" t="n">
-        <v>8</v>
-      </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ9" t="n">
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2821,16 +2821,16 @@
         <v>4.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ9" t="n">
         <v>8</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
         <v>6.2</v>
@@ -2851,14 +2851,14 @@
         <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA9" t="n">
         <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
@@ -2907,7 +2907,7 @@
         <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
@@ -2916,13 +2916,13 @@
         <v>2.68</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
         <v>1.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
@@ -2934,19 +2934,19 @@
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
         <v>75</v>
@@ -2958,7 +2958,7 @@
         <v>7.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
         <v>20</v>
@@ -2997,16 +2997,16 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -3015,10 +3015,10 @@
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3027,31 +3027,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BI10" t="n">
         <v>2.36</v>
@@ -3060,59 +3060,59 @@
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
         <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G11" t="n">
         <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3173,25 +3173,25 @@
         <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
@@ -3200,7 +3200,7 @@
         <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
         <v>50</v>
@@ -3215,19 +3215,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
@@ -3251,16 +3251,16 @@
         <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
         <v>4.9</v>
@@ -3269,34 +3269,34 @@
         <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
         <v>7.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I12" t="n">
         <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3439,16 +3439,16 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
         <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
@@ -3466,7 +3466,7 @@
         <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
@@ -3478,7 +3478,7 @@
         <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH12" t="n">
         <v>500</v>
@@ -3511,10 +3511,10 @@
         <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
@@ -3526,101 +3526,101 @@
         <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
         <v>8.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>1.14</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="BN12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="BT12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3651,76 +3651,76 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.72</v>
       </c>
-      <c r="G13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.68</v>
-      </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
         <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>14.5</v>
@@ -3729,10 +3729,10 @@
         <v>44</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>23</v>
@@ -3768,19 +3768,19 @@
         <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
@@ -3789,22 +3789,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
         <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
         <v>9.800000000000001</v>
@@ -3813,68 +3813,68 @@
         <v>34</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN13" t="n">
         <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP13" t="n">
         <v>29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
         <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU13" t="n">
         <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW13" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>4.8</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
         <v>1.31</v>
       </c>
       <c r="R14" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="T14" t="n">
         <v>1.4</v>
@@ -3953,7 +3953,7 @@
         <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="W14" t="n">
         <v>1.25</v>
@@ -3962,25 +3962,25 @@
         <v>110</v>
       </c>
       <c r="Y14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
         <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB14" t="n">
         <v>80</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
         <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF14" t="n">
         <v>110</v>
@@ -3989,10 +3989,10 @@
         <v>25</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="n">
         <v>490</v>
@@ -4001,37 +4001,37 @@
         <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AP14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT14" t="n">
         <v>26</v>
       </c>
       <c r="AU14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
         <v>11.5</v>
@@ -4040,7 +4040,7 @@
         <v>28</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -4049,7 +4049,7 @@
         <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BC14" t="n">
         <v>29</v>
@@ -4067,7 +4067,7 @@
         <v>4.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI14" t="n">
         <v>4.7</v>
@@ -4085,10 +4085,10 @@
         <v>8.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4109,10 +4109,10 @@
         <v>4.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
         <v>1.56</v>
@@ -4192,7 +4192,7 @@
         <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
@@ -4213,7 +4213,7 @@
         <v>2.12</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y15" t="n">
         <v>14</v>
@@ -4225,7 +4225,7 @@
         <v>250</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -4237,10 +4237,10 @@
         <v>160</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -4252,7 +4252,7 @@
         <v>24</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
         <v>80</v>
@@ -4261,22 +4261,22 @@
         <v>320</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>290</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT15" t="n">
         <v>5.3</v>
@@ -4285,10 +4285,10 @@
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX15" t="n">
         <v>8.4</v>
@@ -4297,28 +4297,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
         <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
         <v>2.68</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-24 22:34:12</t>
+          <t>2026-06-25 00:45:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,37 +857,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
         <v>1.83</v>
@@ -896,28 +896,28 @@
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
         <v>16.5</v>
@@ -926,13 +926,13 @@
         <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
         <v>500</v>
@@ -941,7 +941,7 @@
         <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>80</v>
@@ -965,58 +965,58 @@
         <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
         <v>7.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>19</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
         <v>28</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1046,19 +1046,19 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.26</v>
+        <v>4.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J3" t="n">
         <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="R3" t="n">
         <v>1.89</v>
       </c>
       <c r="S3" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W3" t="n">
         <v>1.11</v>
@@ -1168,10 +1168,10 @@
         <v>130</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
         <v>540</v>
@@ -1201,7 +1201,7 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AK3" t="n">
         <v>160</v>
@@ -1216,70 +1216,70 @@
         <v>530</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
         <v>13</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
         <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BF3" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
         <v>5.9</v>
@@ -1288,28 +1288,28 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>13.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU3" t="n">
         <v>3.45</v>
@@ -1318,13 +1318,13 @@
         <v>7.6</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX3" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1368,97 +1368,97 @@
         <v>1.47</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>5.2</v>
       </c>
-      <c r="I4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.3</v>
-      </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S4" t="n">
         <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
         <v>170</v>
       </c>
       <c r="Y4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z4" t="n">
         <v>170</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AC4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
         <v>21</v>
@@ -1467,128 +1467,128 @@
         <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>14</v>
+        <v>5.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AW4" t="n">
         <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>15.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL4" t="n">
         <v>48</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
         <v>15</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BT4" t="n">
         <v>11.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1622,97 +1622,97 @@
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
         <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,10 +1721,10 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1733,10 +1733,10 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
@@ -1745,76 +1745,76 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="n">
         <v>3.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT5" t="n">
         <v>5.7</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -1873,55 +1873,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
         <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -1975,10 +1975,10 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>4.2</v>
@@ -1987,46 +1987,46 @@
         <v>1.31</v>
       </c>
       <c r="AR6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS6" t="n">
         <v>1.33</v>
       </c>
-      <c r="AS6" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AT6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AU6" t="n">
         <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AX6" t="n">
         <v>1.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF6" t="n">
         <v>1.55</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2154,55 +2154,55 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
         <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>27</v>
       </c>
       <c r="AB7" t="n">
         <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
         <v>100</v>
@@ -2211,10 +2211,10 @@
         <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2235,122 +2235,122 @@
         <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.7</v>
+        <v>1.98</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.52</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.49</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,164 +2447,164 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB8" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="BC8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BO8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2635,100 +2635,100 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
         <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
         <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
         <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>190</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
         <v>460</v>
@@ -2737,40 +2737,40 @@
         <v>500</v>
       </c>
       <c r="AN9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO9" t="n">
         <v>65</v>
       </c>
-      <c r="AO9" t="n">
-        <v>75</v>
-      </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
         <v>15.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
@@ -2782,64 +2782,64 @@
         <v>8.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP9" t="n">
         <v>30</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9" t="n">
         <v>60</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW9" t="n">
         <v>8.199999999999999</v>
@@ -2848,17 +2848,17 @@
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
         <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.56</v>
@@ -2913,43 +2913,43 @@
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2967,46 +2967,46 @@
         <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AL10" t="n">
         <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -3015,49 +3015,49 @@
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY10" t="n">
         <v>10</v>
       </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
         <v>6.6</v>
@@ -3066,13 +3066,13 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
@@ -3090,19 +3090,19 @@
         <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3143,115 +3143,115 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>50</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AI11" t="n">
         <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="n">
-        <v>230</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.1</v>
@@ -3260,43 +3260,43 @@
         <v>6.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
         <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
         <v>7.8</v>
@@ -3305,68 +3305,68 @@
         <v>8.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
@@ -3463,7 +3463,7 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
         <v>15</v>
@@ -3487,7 +3487,7 @@
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="AK12" t="n">
         <v>500</v>
@@ -3499,10 +3499,10 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
         <v>4.4</v>
@@ -3511,116 +3511,116 @@
         <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV12" t="n">
         <v>7.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.5</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BA12" t="n">
-        <v>8.6</v>
+        <v>3.45</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.6</v>
+        <v>3.45</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG12" t="n">
         <v>8.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.16</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3651,103 +3651,103 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
         <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
@@ -3759,61 +3759,61 @@
         <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AU13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA13" t="n">
         <v>6</v>
       </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
+      <c r="BB13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD13" t="n">
         <v>6</v>
       </c>
-      <c r="BA13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>34</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BI13" t="n">
         <v>2.3</v>
@@ -3822,13 +3822,13 @@
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>2.16</v>
       </c>
       <c r="BN13" t="n">
         <v>6.2</v>
@@ -3840,41 +3840,41 @@
         <v>29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13" t="n">
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G14" t="n">
         <v>5</v>
@@ -3914,46 +3914,46 @@
         <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="T14" t="n">
         <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W14" t="n">
         <v>1.25</v>
@@ -3968,13 +3968,13 @@
         <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AB14" t="n">
         <v>80</v>
       </c>
       <c r="AC14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD14" t="n">
         <v>12.5</v>
@@ -3986,10 +3986,10 @@
         <v>110</v>
       </c>
       <c r="AG14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AI14" t="n">
         <v>20</v>
@@ -4001,37 +4001,37 @@
         <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AN14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ14" t="n">
         <v>15.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AU14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW14" t="n">
         <v>11.5</v>
@@ -4043,31 +4043,31 @@
         <v>18</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
         <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BC14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD14" t="n">
         <v>29</v>
       </c>
-      <c r="BD14" t="n">
-        <v>22</v>
-      </c>
       <c r="BE14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI14" t="n">
         <v>4.7</v>
@@ -4076,34 +4076,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU14" t="n">
         <v>4.2</v>
@@ -4112,13 +4112,13 @@
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
         <v>5.7</v>
@@ -4174,58 +4174,58 @@
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
         <v>1.56</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
         <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
         <v>1.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X15" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="n">
         <v>250</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -4234,7 +4234,7 @@
         <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF15" t="n">
         <v>9.4</v>
@@ -4246,7 +4246,7 @@
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ15" t="n">
         <v>24</v>
@@ -4255,16 +4255,16 @@
         <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN15" t="n">
         <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP15" t="n">
         <v>7.8</v>
@@ -4273,116 +4273,116 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
         <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BA15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>11</v>
-      </c>
       <c r="BF15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="n">
         <v>2.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO15" t="n">
         <v>3.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>13.5</v>
+        <v>2.28</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 00:45:14</t>
+          <t>2026-06-25 02:56:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,34 +857,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
         <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.1</v>
@@ -896,43 +896,43 @@
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AA2" t="n">
         <v>16.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
         <v>500</v>
@@ -941,10 +941,10 @@
         <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>700</v>
@@ -959,13 +959,13 @@
         <v>700</v>
       </c>
       <c r="AN2" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="AO2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>7.2</v>
@@ -974,7 +974,7 @@
         <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
         <v>19</v>
@@ -983,49 +983,49 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
         <v>28</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
         <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
         <v>8.199999999999999</v>
@@ -1034,10 +1034,10 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO2" t="n">
         <v>7.4</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT2" t="n">
         <v>4.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1135,64 +1135,64 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF3" t="n">
         <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
@@ -1201,10 +1201,10 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AK3" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AL3" t="n">
         <v>390</v>
@@ -1213,10 +1213,10 @@
         <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
@@ -1225,25 +1225,25 @@
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS3" t="n">
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AU3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>16.5</v>
@@ -1252,79 +1252,79 @@
         <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
         <v>28</v>
       </c>
       <c r="BE3" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BV3" t="n">
         <v>7.6</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="BX3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1365,40 +1365,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
         <v>6.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O4" t="n">
         <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R4" t="n">
         <v>2.42</v>
@@ -1407,16 +1407,16 @@
         <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X4" t="n">
         <v>170</v>
@@ -1431,7 +1431,7 @@
         <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="n">
         <v>22</v>
@@ -1443,10 +1443,10 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>19</v>
@@ -1455,7 +1455,7 @@
         <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
@@ -1470,125 +1470,125 @@
         <v>3.55</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>2.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL4" t="n">
         <v>48</v>
       </c>
       <c r="BM4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
         <v>15</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>36</v>
       </c>
       <c r="BW4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY4" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>7</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1652,22 +1652,22 @@
         <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
         <v>1.46</v>
@@ -1679,25 +1679,25 @@
         <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB5" t="n">
         <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
         <v>16</v>
@@ -1712,43 +1712,43 @@
         <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>75</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1757,7 +1757,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
         <v>32</v>
@@ -1766,16 +1766,16 @@
         <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
         <v>17</v>
@@ -1784,19 +1784,19 @@
         <v>3.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>6.4</v>
@@ -1808,16 +1808,16 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU5" t="n">
         <v>4.2</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -1873,55 +1873,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
         <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -1975,7 +1975,7 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
@@ -1984,10 +1984,10 @@
         <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.32</v>
       </c>
       <c r="AS6" t="n">
         <v>1.33</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2145,76 +2145,76 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
         <v>2.42</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
         <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
         <v>100</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2223,7 +2223,7 @@
         <v>470</v>
       </c>
       <c r="AL7" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
@@ -2232,25 +2232,25 @@
         <v>700</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
         <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>8.4</v>
@@ -2259,10 +2259,10 @@
         <v>18</v>
       </c>
       <c r="AX7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>15</v>
       </c>
       <c r="AZ7" t="n">
         <v>19</v>
@@ -2271,40 +2271,40 @@
         <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH7" t="n">
         <v>2.98</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
         <v>8.199999999999999</v>
@@ -2316,41 +2316,41 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.95</v>
+        <v>9.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.98</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2381,67 +2381,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
         <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.62</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.72</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
         <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,7 +2450,7 @@
         <v>6.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>48</v>
@@ -2462,19 +2462,19 @@
         <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,128 +2483,128 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>410</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK8" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
         <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2635,76 +2635,76 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
         <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
         <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="n">
         <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
         <v>15</v>
@@ -2713,7 +2713,7 @@
         <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
@@ -2725,13 +2725,13 @@
         <v>190</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="n">
         <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
@@ -2740,16 +2740,16 @@
         <v>70</v>
       </c>
       <c r="AO9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
         <v>18</v>
@@ -2758,52 +2758,52 @@
         <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX9" t="n">
         <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
         <v>8.800000000000001</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>6</v>
@@ -2821,25 +2821,25 @@
         <v>5</v>
       </c>
       <c r="BP9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>6</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
         <v>8.199999999999999</v>
@@ -2848,17 +2848,17 @@
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.56</v>
@@ -2913,10 +2913,10 @@
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
         <v>1.57</v>
@@ -2928,49 +2928,49 @@
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>32</v>
@@ -2979,140 +2979,140 @@
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
         <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU10" t="n">
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF10" t="n">
         <v>23</v>
       </c>
-      <c r="BC10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>24</v>
-      </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH10" t="n">
         <v>2.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU10" t="n">
         <v>6</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3143,169 +3143,169 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
         <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="X11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
         <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>30</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
         <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="BI11" t="n">
         <v>2.32</v>
@@ -3314,59 +3314,59 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.2</v>
+        <v>11.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.12</v>
+        <v>9.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
         <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.64</v>
@@ -3421,16 +3421,16 @@
         <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P12" t="n">
         <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
@@ -3439,10 +3439,10 @@
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
         <v>1.5</v>
@@ -3451,10 +3451,10 @@
         <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z12" t="n">
         <v>970</v>
@@ -3463,7 +3463,7 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="AC12" t="n">
         <v>15</v>
@@ -3499,7 +3499,7 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
@@ -3511,55 +3511,55 @@
         <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>8.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="BG12" t="n">
         <v>8.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BI12" t="n">
         <v>2.14</v>
@@ -3568,59 +3568,59 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.6</v>
+        <v>1.27</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3651,169 +3651,169 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="n">
         <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO13" t="n">
         <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BI13" t="n">
         <v>2.3</v>
@@ -3822,59 +3822,59 @@
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.16</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
         <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
         <v>29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
         <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>29</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -3938,19 +3938,19 @@
         <v>3.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
         <v>2.44</v>
@@ -3962,7 +3962,7 @@
         <v>110</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
         <v>19.5</v>
@@ -3974,70 +3974,70 @@
         <v>80</v>
       </c>
       <c r="AC14" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF14" t="n">
         <v>110</v>
       </c>
       <c r="AG14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="n">
-        <v>490</v>
+        <v>330</v>
       </c>
       <c r="AK14" t="n">
         <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AP14" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR14" t="n">
         <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AU14" t="n">
         <v>12</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
         <v>11.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AY14" t="n">
         <v>18</v>
@@ -4046,22 +4046,22 @@
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>40</v>
       </c>
       <c r="BC14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD14" t="n">
         <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
         <v>4.3</v>
@@ -4070,37 +4070,37 @@
         <v>6.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN14" t="n">
         <v>9.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>8</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
         <v>5.6</v>
@@ -4112,7 +4112,7 @@
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -4186,7 +4186,7 @@
         <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P15" t="n">
         <v>1.54</v>
@@ -4195,13 +4195,13 @@
         <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
         <v>1.65</v>
@@ -4210,7 +4210,7 @@
         <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X15" t="n">
         <v>11</v>
@@ -4225,7 +4225,7 @@
         <v>250</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -4243,7 +4243,7 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
         <v>170</v>
@@ -4273,13 +4273,13 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
@@ -4288,37 +4288,37 @@
         <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
         <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
         <v>18.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
         <v>2.68</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 02:56:45</t>
+          <t>2026-06-25 05:08:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -875,37 +875,37 @@
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
@@ -914,10 +914,10 @@
         <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
         <v>16.5</v>
@@ -926,22 +926,22 @@
         <v>48</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AG2" t="n">
         <v>55</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>46</v>
@@ -950,7 +950,7 @@
         <v>700</v>
       </c>
       <c r="AK2" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AL2" t="n">
         <v>700</v>
@@ -959,28 +959,28 @@
         <v>700</v>
       </c>
       <c r="AN2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>19</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
         <v>8.4</v>
@@ -989,43 +989,43 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>28</v>
       </c>
-      <c r="BD2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>11</v>
-      </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
         <v>8.199999999999999</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>11</v>
@@ -1046,22 +1046,22 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
         <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW2" t="n">
         <v>8.199999999999999</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1111,130 +1111,130 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="I3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K3" t="n">
         <v>6.4</v>
       </c>
-      <c r="K3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.13</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
         <v>120</v>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
         <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="AK3" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AL3" t="n">
         <v>390</v>
       </c>
       <c r="AM3" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO3" t="n">
         <v>4.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10</v>
-      </c>
       <c r="AT3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
         <v>8.800000000000001</v>
@@ -1243,88 +1243,88 @@
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="AY3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
       </c>
       <c r="BF3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>13.5</v>
       </c>
-      <c r="BG3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BN3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU3" t="n">
         <v>3.95</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.92</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>1.13</v>
@@ -1389,40 +1389,40 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="R4" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
         <v>170</v>
       </c>
       <c r="Y4" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="Z4" t="n">
         <v>170</v>
@@ -1431,7 +1431,7 @@
         <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
         <v>22</v>
@@ -1443,19 +1443,19 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
         <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
@@ -1464,49 +1464,49 @@
         <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1515,80 +1515,80 @@
         <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
         <v>2.82</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BT4" t="n">
         <v>12</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
@@ -1646,46 +1646,46 @@
         <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
         <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
         <v>7.8</v>
@@ -1694,10 +1694,10 @@
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
         <v>16</v>
@@ -1709,10 +1709,10 @@
         <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AK5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="n">
         <v>290</v>
@@ -1721,61 +1721,61 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO5" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB5" t="n">
         <v>32</v>
       </c>
-      <c r="BB5" t="n">
-        <v>36</v>
-      </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
         <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BG5" t="n">
         <v>17</v>
@@ -1784,37 +1784,37 @@
         <v>3.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
         <v>5.8</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L6" t="n">
         <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
         <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
         <v>2.8</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T6" t="n">
         <v>1.79</v>
@@ -1921,10 +1921,10 @@
         <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1984,49 +1984,49 @@
         <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AS6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT6" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.31</v>
       </c>
       <c r="AU6" t="n">
         <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.33</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
         <v>1.55</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2127,82 +2127,82 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
         <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
         <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
         <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB7" t="n">
         <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
         <v>100</v>
@@ -2211,16 +2211,16 @@
         <v>40</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>470</v>
+        <v>200</v>
       </c>
       <c r="AL7" t="n">
         <v>700</v>
@@ -2229,25 +2229,25 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AO7" t="n">
         <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT7" t="n">
         <v>11</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
@@ -2256,7 +2256,7 @@
         <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX7" t="n">
         <v>16.5</v>
@@ -2265,52 +2265,52 @@
         <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>11</v>
       </c>
-      <c r="BC7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,29 +2328,29 @@
         <v>4.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G8" t="n">
         <v>1.92</v>
@@ -2390,16 +2390,16 @@
         <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -2408,28 +2408,28 @@
         <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T8" t="n">
         <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
         <v>2.08</v>
@@ -2441,7 +2441,7 @@
         <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,16 +2450,16 @@
         <v>6.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2474,7 +2474,7 @@
         <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,10 +2483,10 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="AP8" t="n">
         <v>7.4</v>
@@ -2498,7 +2498,7 @@
         <v>29</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
@@ -2513,31 +2513,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BB8" t="n">
         <v>16.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE8" t="n">
         <v>8.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG8" t="n">
         <v>8.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2638,37 +2638,37 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="K9" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="L9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P9" t="n">
         <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R9" t="n">
         <v>1.16</v>
@@ -2677,16 +2677,16 @@
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
         <v>7.8</v>
@@ -2695,13 +2695,13 @@
         <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
         <v>7.2</v>
@@ -2710,7 +2710,7 @@
         <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
         <v>19</v>
@@ -2722,16 +2722,16 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AK9" t="n">
         <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
@@ -2776,7 +2776,7 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
         <v>23</v>
@@ -2788,13 +2788,13 @@
         <v>29</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>2.62</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
         <v>3.95</v>
@@ -2901,10 +2901,10 @@
         <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
         <v>1.56</v>
@@ -2913,7 +2913,7 @@
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
         <v>1.52</v>
@@ -2922,7 +2922,7 @@
         <v>1.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
@@ -2934,19 +2934,19 @@
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.76</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.78</v>
       </c>
       <c r="X10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
         <v>32</v>
@@ -2982,7 +2982,7 @@
         <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL10" t="n">
         <v>150</v>
@@ -3003,7 +3003,7 @@
         <v>9.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS10" t="n">
         <v>9.6</v>
@@ -3030,7 +3030,7 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>22</v>
@@ -3039,7 +3039,7 @@
         <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE10" t="n">
         <v>10</v>
@@ -3051,7 +3051,7 @@
         <v>9.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI10" t="n">
         <v>2.5</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
         <v>4.9</v>
@@ -3078,7 +3078,7 @@
         <v>24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3102,17 +3102,17 @@
         <v>75</v>
       </c>
       <c r="BY10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
         <v>3.35</v>
@@ -3158,10 +3158,10 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M11" t="n">
         <v>1.12</v>
@@ -3170,13 +3170,13 @@
         <v>2.66</v>
       </c>
       <c r="O11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.55</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.54</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
         <v>1.19</v>
@@ -3185,25 +3185,25 @@
         <v>5.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
         <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
         <v>85</v>
@@ -3215,13 +3215,13 @@
         <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
         <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3230,10 +3230,10 @@
         <v>30</v>
       </c>
       <c r="AI11" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK11" t="n">
         <v>44</v>
@@ -3242,16 +3242,16 @@
         <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AN11" t="n">
         <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.4</v>
@@ -3269,10 +3269,10 @@
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
@@ -3293,13 +3293,13 @@
         <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BG11" t="n">
         <v>46</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3403,16 +3403,16 @@
         <v>3.15</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.64</v>
@@ -3421,16 +3421,16 @@
         <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
         <v>1.61</v>
       </c>
       <c r="P12" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
@@ -3439,58 +3439,58 @@
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="n">
-        <v>500</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG12" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AH12" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,128 +3499,128 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
         <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.56</v>
+        <v>42</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3651,61 +3651,61 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.92</v>
       </c>
-      <c r="G13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.9</v>
-      </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.96</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
         <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
         <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="n">
         <v>9.199999999999999</v>
@@ -3714,22 +3714,22 @@
         <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
         <v>14.5</v>
@@ -3768,7 +3768,7 @@
         <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="AT13" t="n">
         <v>7.4</v>
@@ -3780,10 +3780,10 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
@@ -3792,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
         <v>38</v>
@@ -3801,13 +3801,13 @@
         <v>34</v>
       </c>
       <c r="BD13" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE13" t="n">
         <v>28</v>
       </c>
-      <c r="BE13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BG13" t="n">
         <v>36</v>
@@ -3834,7 +3834,7 @@
         <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP13" t="n">
         <v>29</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>4.7</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H14" t="n">
         <v>1.65</v>
@@ -3920,7 +3920,7 @@
         <v>4.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.19</v>
@@ -3929,43 +3929,43 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="R14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T14" t="n">
         <v>1.41</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V14" t="n">
         <v>2.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
         <v>110</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>22</v>
@@ -3974,7 +3974,7 @@
         <v>80</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
@@ -4001,7 +4001,7 @@
         <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
         <v>100</v>
@@ -4022,7 +4022,7 @@
         <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
         <v>32</v>
@@ -4040,16 +4040,16 @@
         <v>44</v>
       </c>
       <c r="AY14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB14" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BC14" t="n">
         <v>38</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>1.83</v>
       </c>
       <c r="G15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
@@ -4183,16 +4183,16 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
         <v>1.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
@@ -4201,7 +4201,7 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U15" t="n">
         <v>1.65</v>
@@ -4264,7 +4264,7 @@
         <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AP15" t="n">
         <v>7.8</v>
@@ -4282,10 +4282,10 @@
         <v>5.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
         <v>8.199999999999999</v>
@@ -4309,10 +4309,10 @@
         <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
         <v>18.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 05:08:13</t>
+          <t>2026-06-25 07:19:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>7.8</v>
@@ -869,25 +869,25 @@
         <v>1.58</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
         <v>1.81</v>
@@ -896,28 +896,28 @@
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>2.72</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AA2" t="n">
         <v>16.5</v>
@@ -929,158 +929,158 @@
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>270</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>700</v>
       </c>
       <c r="AK2" t="n">
-        <v>480</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
       <c r="AM2" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="AN2" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AO2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF2" t="n">
         <v>11</v>
       </c>
-      <c r="BC2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>34</v>
-      </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
         <v>11</v>
       </c>
       <c r="BO2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA2" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -1111,97 +1111,97 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
         <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
         <v>11.5</v>
       </c>
       <c r="AA3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC3" t="n">
         <v>15</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AG3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AK3" t="n">
         <v>260</v>
@@ -1210,19 +1210,19 @@
         <v>390</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>790</v>
       </c>
       <c r="AN3" t="n">
         <v>110</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>10</v>
@@ -1231,46 +1231,46 @@
         <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX3" t="n">
         <v>40</v>
       </c>
       <c r="AY3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>17</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
         <v>60</v>
       </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
         <v>46</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH3" t="n">
         <v>5.2</v>
@@ -1279,7 +1279,7 @@
         <v>4.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
         <v>6.2</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BN3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1312,19 +1312,19 @@
         <v>4.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K4" t="n">
         <v>7</v>
@@ -1389,46 +1389,46 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="R4" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
         <v>170</v>
       </c>
       <c r="Y4" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AA4" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
         <v>32</v>
@@ -1437,25 +1437,25 @@
         <v>22</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
@@ -1464,73 +1464,73 @@
         <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="n">
         <v>17</v>
       </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
@@ -1539,56 +1539,56 @@
         <v>7.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BM4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
         <v>14</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT4" t="n">
         <v>12</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.88</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
@@ -1643,16 +1643,16 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
         <v>1.31</v>
@@ -1661,31 +1661,31 @@
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
         <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>7.8</v>
@@ -1697,43 +1697,43 @@
         <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
         <v>27</v>
@@ -1748,7 +1748,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1757,46 +1757,46 @@
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB5" t="n">
         <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
         <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG5" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
         <v>10</v>
       </c>
       <c r="BK5" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1805,16 +1805,16 @@
         <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>5.8</v>
@@ -1823,16 +1823,16 @@
         <v>4.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
         <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
         <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1984,49 +1984,49 @@
         <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AS6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT6" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.33</v>
       </c>
       <c r="AU6" t="n">
         <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.36</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.36</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BF6" t="n">
         <v>1.55</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -2127,73 +2127,73 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Z7" t="n">
         <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
         <v>8.199999999999999</v>
@@ -2202,19 +2202,19 @@
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
         <v>100</v>
       </c>
       <c r="AG7" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
         <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2229,128 +2229,128 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
         <v>46</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11</v>
-      </c>
       <c r="BN7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>4.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -2405,16 +2405,16 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
         <v>1.53</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -2423,10 +2423,10 @@
         <v>5.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -2435,13 +2435,13 @@
         <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2453,7 +2453,7 @@
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
@@ -2474,28 +2474,28 @@
         <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="AP8" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS8" t="n">
         <v>8.4</v>
@@ -2507,28 +2507,28 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
         <v>9.199999999999999</v>
@@ -2543,7 +2543,7 @@
         <v>8.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI8" t="n">
         <v>2.28</v>
@@ -2558,28 +2558,28 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8" t="n">
         <v>4.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
         <v>2.74</v>
       </c>
       <c r="K9" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
         <v>1.16</v>
@@ -2662,13 +2662,13 @@
         <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P9" t="n">
         <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1.16</v>
@@ -2680,10 +2680,10 @@
         <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
         <v>1.44</v>
@@ -2692,31 +2692,31 @@
         <v>7.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>26</v>
@@ -2728,137 +2728,137 @@
         <v>95</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>7</v>
-      </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB9" t="n">
         <v>23</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BH9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK9" t="n">
+      <c r="BR9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW9" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -2889,217 +2889,217 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>1.88</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU10" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>12</v>
-      </c>
       <c r="BN10" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
         <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BY10" t="n">
         <v>10.5</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -3143,88 +3143,88 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>30</v>
@@ -3233,140 +3233,140 @@
         <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AK11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>70</v>
       </c>
-      <c r="AM11" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BH11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="BU11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>46</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BV11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
         <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>2.98</v>
       </c>
       <c r="G12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K12" t="n">
         <v>3.1</v>
@@ -3421,76 +3421,76 @@
         <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.61</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="AK12" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
@@ -3499,67 +3499,67 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA12" t="n">
         <v>5.5</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ12" t="n">
+      <c r="BB12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BC12" t="n">
         <v>18</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>30</v>
       </c>
       <c r="BD12" t="n">
         <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>2.96</v>
       </c>
       <c r="BF12" t="n">
-        <v>42</v>
+        <v>2.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>14</v>
+        <v>2.74</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BI12" t="n">
         <v>2.2</v>
@@ -3568,31 +3568,31 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I13" t="n">
         <v>3.2</v>
@@ -3675,16 +3675,16 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.66</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.62</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
@@ -3696,13 +3696,13 @@
         <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
         <v>9</v>
@@ -3711,13 +3711,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
         <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
         <v>7.6</v>
@@ -3726,155 +3726,155 @@
         <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
         <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
         <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO13" t="n">
         <v>60</v>
       </c>
-      <c r="AO13" t="n">
-        <v>55</v>
-      </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS13" t="n">
         <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BD13" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>38</v>
       </c>
       <c r="BG13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR13" t="n">
         <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT13" t="n">
         <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>55</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H14" t="n">
         <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.19</v>
@@ -3929,67 +3929,67 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="T14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="Y14" t="n">
         <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB14" t="n">
         <v>80</v>
       </c>
       <c r="AC14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
       </c>
       <c r="AE14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH14" t="n">
         <v>15</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>15.5</v>
       </c>
       <c r="AI14" t="n">
         <v>21</v>
@@ -3998,64 +3998,64 @@
         <v>330</v>
       </c>
       <c r="AK14" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR14" t="n">
         <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AY14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB14" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="BC14" t="n">
         <v>38</v>
       </c>
       <c r="BD14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>34</v>
@@ -4064,10 +4064,10 @@
         <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI14" t="n">
         <v>4.8</v>
@@ -4076,34 +4076,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU14" t="n">
         <v>4.2</v>
@@ -4112,13 +4112,13 @@
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>
@@ -4162,70 +4162,70 @@
         <v>1.83</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H15" t="n">
         <v>5.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
         <v>2.14</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AA15" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -4234,37 +4234,37 @@
         <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF15" t="n">
         <v>9.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>32</v>
       </c>
       <c r="AI15" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
         <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AP15" t="n">
         <v>7.8</v>
@@ -4273,10 +4273,10 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>5.3</v>
@@ -4285,58 +4285,58 @@
         <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AX15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC15" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7</v>
-      </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN15" t="n">
         <v>4.1</v>
@@ -4345,7 +4345,7 @@
         <v>3.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ15" t="n">
         <v>8.4</v>
@@ -4357,22 +4357,22 @@
         <v>13</v>
       </c>
       <c r="BT15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU15" t="n">
         <v>6.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.28</v>
+        <v>15</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 07:19:53</t>
+          <t>2026-06-25 09:35:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>410</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>360</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU2" t="n">
         <v>7.8</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="AV2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>170</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BI2" t="n">
         <v>1.14</v>
       </c>
-      <c r="X2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>230</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>940</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="BJ2" t="n">
+        <v>280</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>240</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>4.2</v>
       </c>
-      <c r="BU2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1111,217 +1111,217 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="G3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K3" t="n">
         <v>6.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Y3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC3" t="n">
         <v>14</v>
       </c>
-      <c r="Z3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AF3" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AJ3" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="AK3" t="n">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AL3" t="n">
         <v>390</v>
       </c>
       <c r="AM3" t="n">
-        <v>790</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AU3" t="n">
         <v>12.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AX3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>46</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO3" t="n">
+      <c r="BT3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BW3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="BY3" t="n">
         <v>8.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="n">
         <v>6.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.13</v>
@@ -1389,73 +1389,73 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
         <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X4" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z4" t="n">
         <v>170</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>180</v>
       </c>
       <c r="AA4" t="n">
         <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>15.5</v>
@@ -1464,73 +1464,73 @@
         <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE4" t="n">
         <v>20</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
@@ -1539,16 +1539,16 @@
         <v>7.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
         <v>9.199999999999999</v>
@@ -1557,19 +1557,19 @@
         <v>7.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT4" t="n">
         <v>12</v>
       </c>
       <c r="BU4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
         <v>7</v>
@@ -1581,14 +1581,14 @@
         <v>6.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
         <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1655,22 +1655,22 @@
         <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
         <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1691,10 +1691,10 @@
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
@@ -1712,10 +1712,10 @@
         <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>200</v>
@@ -1730,13 +1730,13 @@
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT5" t="n">
         <v>9.800000000000001</v>
@@ -1745,7 +1745,7 @@
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1766,31 +1766,31 @@
         <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
         <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
         <v>18.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI5" t="n">
         <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,49 +1915,49 @@
         <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1966,7 +1966,7 @@
         <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
@@ -1975,64 +1975,64 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.39</v>
+        <v>22</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.36</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.39</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.36</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.36</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.39</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.39</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.39</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.39</v>
+        <v>5.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.55</v>
+        <v>36</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>22</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2044,59 +2044,59 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2127,100 +2127,100 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="I7" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.89</v>
       </c>
-      <c r="V7" t="n">
-        <v>2.08</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
         <v>8.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
         <v>100</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>200</v>
+        <v>470</v>
       </c>
       <c r="AL7" t="n">
         <v>700</v>
@@ -2229,109 +2229,109 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AX7" t="n">
-        <v>27</v>
-      </c>
       <c r="AY7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
         <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
         <v>10</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G8" t="n">
         <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
         <v>2.72</v>
@@ -2411,25 +2411,25 @@
         <v>1.53</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
         <v>2.08</v>
@@ -2438,10 +2438,10 @@
         <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2486,7 +2486,7 @@
         <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AP8" t="n">
         <v>7.4</v>
@@ -2498,7 +2498,7 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
@@ -2510,7 +2510,7 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2519,22 +2519,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>16</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
         <v>17</v>
@@ -2543,7 +2543,7 @@
         <v>8.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI8" t="n">
         <v>2.28</v>
@@ -2552,13 +2552,13 @@
         <v>13</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
         <v>4.5</v>
@@ -2570,41 +2570,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2641,16 +2641,16 @@
         <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="L9" t="n">
         <v>1.66</v>
@@ -2662,7 +2662,7 @@
         <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P9" t="n">
         <v>1.45</v>
@@ -2677,19 +2677,19 @@
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2722,7 +2722,7 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
         <v>95</v>
@@ -2740,13 +2740,13 @@
         <v>210</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AP9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
         <v>14.5</v>
@@ -2758,7 +2758,7 @@
         <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
@@ -2776,7 +2776,7 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BB9" t="n">
         <v>23</v>
@@ -2785,7 +2785,7 @@
         <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BE9" t="n">
         <v>10.5</v>
@@ -2797,13 +2797,13 @@
         <v>9.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
         <v>7.6</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>5.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
         <v>28</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>65</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2916,64 +2916,64 @@
         <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2982,73 +2982,73 @@
         <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
         <v>16</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3057,62 +3057,62 @@
         <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>7</v>
       </c>
       <c r="BR10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT10" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>10</v>
       </c>
-      <c r="BX10" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA10" t="n">
         <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="G11" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
         <v>2.14</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
         <v>25</v>
       </c>
-      <c r="AK11" t="n">
-        <v>38</v>
-      </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS11" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AX11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
         <v>34</v>
       </c>
       <c r="BE11" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BO11" t="n">
         <v>3.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I12" t="n">
         <v>2.98</v>
       </c>
-      <c r="G12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3</v>
-      </c>
       <c r="J12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
         <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
         <v>1.14</v>
@@ -3439,19 +3439,19 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="V12" t="n">
         <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -3463,10 +3463,10 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
@@ -3508,28 +3508,28 @@
         <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR12" t="n">
         <v>8.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>7.6</v>
@@ -3538,28 +3538,28 @@
         <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.88</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI12" t="n">
         <v>2.2</v>
@@ -3568,13 +3568,13 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
@@ -3586,19 +3586,19 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3610,17 +3610,17 @@
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="n">
         <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I13" t="n">
         <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
@@ -3675,10 +3675,10 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
         <v>1.54</v>
@@ -3690,13 +3690,13 @@
         <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T13" t="n">
         <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
         <v>1.45</v>
@@ -3705,16 +3705,16 @@
         <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
         <v>9</v>
@@ -3723,7 +3723,7 @@
         <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>55</v>
@@ -3756,22 +3756,22 @@
         <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
@@ -3780,49 +3780,49 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AX13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA13" t="n">
         <v>15</v>
       </c>
-      <c r="AY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>46</v>
-      </c>
       <c r="BB13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC13" t="n">
         <v>34</v>
       </c>
-      <c r="BC13" t="n">
-        <v>29</v>
-      </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="n">
         <v>2.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="BJ13" t="n">
         <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,7 +3834,7 @@
         <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP13" t="n">
         <v>28</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -3905,154 +3905,154 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.65</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.67</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="S14" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y14" t="n">
         <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AC14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE14" t="n">
         <v>14.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
         <v>38</v>
       </c>
       <c r="AM14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AP14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
       </c>
       <c r="AX14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC14" t="n">
         <v>50</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>95</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>38</v>
       </c>
       <c r="BD14" t="n">
         <v>34</v>
@@ -4061,64 +4061,64 @@
         <v>34</v>
       </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BN14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BO14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS14" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
         <v>5.7</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV14" t="n">
         <v>10.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>5.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -4192,22 +4192,22 @@
         <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
         <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
         <v>2.14</v>
@@ -4219,7 +4219,7 @@
         <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="n">
         <v>270</v>
@@ -4363,7 +4363,7 @@
         <v>6.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
         <v>15</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-25 09:35:09</t>
+          <t>2026-06-25 11:50:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,498 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4</v>
+        <v>1.86</v>
       </c>
       <c r="H2" t="n">
-        <v>1.42</v>
+        <v>5.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.43</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>6.2</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.46</v>
+        <v>2.42</v>
       </c>
       <c r="U2" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>3.25</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>2.16</v>
       </c>
       <c r="X2" t="n">
-        <v>85</v>
+        <v>8.4</v>
       </c>
       <c r="Y2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW2" t="n">
         <v>20</v>
       </c>
-      <c r="Z2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AX2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>510</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>24</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BA2" t="n">
         <v>18</v>
       </c>
       <c r="BB2" t="n">
-        <v>75</v>
+        <v>18.5</v>
       </c>
       <c r="BC2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD2" t="n">
         <v>32</v>
       </c>
-      <c r="BD2" t="n">
-        <v>36</v>
-      </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="BF2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.3</v>
+        <v>19</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.5</v>
+        <v>2.64</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.7</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.11</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>42</v>
+        <v>2.32</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.11</v>
+        <v>8.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.11</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.11</v>
+        <v>6.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.11</v>
+        <v>16.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 16:22:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Cuiaba</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-25 16:22:34</t>
+          <t>2026-06-25 18:37:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8</v>
+        <v>2.52</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.35</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="T2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.59</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.19</v>
-      </c>
       <c r="W2" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
         <v>14</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AS2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA2" t="n">
         <v>48</v>
       </c>
-      <c r="AA2" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>26</v>
       </c>
-      <c r="AE2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="BE2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF2" t="n">
         <v>24</v>
       </c>
-      <c r="AO2" t="n">
-        <v>320</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BG2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
         <v>18</v>
       </c>
-      <c r="BB2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="BL2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1000</v>
       </c>
-      <c r="BM2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="BP2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BS2" t="n">
         <v>13.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.199999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.2</v>
+        <v>2.12</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.26</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA2" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-25 18:37:41</t>
+          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Cuiaba</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>44</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>28</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-25 20:53:07</t>
         </is>
       </c>
     </row>
